--- a/mario/test/supporting_files/cvxlab/mario_add_sector_split/sets.xlsx
+++ b/mario/test/supporting_files/cvxlab/mario_add_sector_split/sets.xlsx
@@ -12,7 +12,8 @@
     <sheet name="_set_REGION_FROM" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="_set_REGION_TO" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="_set_CONS_CATEG" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="_set_SCALAR" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="_set_FACTOR" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="_set_SCALAR" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,6 +689,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>factor_Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wages</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
